--- a/patchr/resources/PLATES_v2.0.0/CB[BATCH_ID].xlsx
+++ b/patchr/resources/PLATES_v2.0.0/CB[BATCH_ID].xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10212"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11008"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/analysis/resources/PLATES_v2.0.0/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tpd0001/github/watch-wv/patchr/resources/PLATES_v2.0.0/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4D7259A-0168-5F44-B971-D575F84CCE83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DCE4B5B3-CFE3-C443-B072-6D08E088827B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1240" yWindow="760" windowWidth="27080" windowHeight="15980" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1240" yWindow="760" windowWidth="27080" windowHeight="15980" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Metadata" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="71">
   <si>
     <t>Concentration</t>
   </si>
@@ -93,12 +93,6 @@
   </si>
   <si>
     <t>Wall-E</t>
-  </si>
-  <si>
-    <t>Ceres Nanotrap Magnetic Virus Particles</t>
-  </si>
-  <si>
-    <t>Ceres Nanotrap Magnetic Microbiome B Particles</t>
   </si>
   <si>
     <t>Run By</t>
@@ -247,16 +241,35 @@
   <si>
     <t>&lt;- Enter the amount of spike-in, in total copies added. For biological or genomic spikes this is copies of the genome.</t>
   </si>
+  <si>
+    <t>Ceres Nanotrap Magnetic Microbiome A Particles</t>
+  </si>
+  <si>
+    <t>Ceres Nanotrap Microbiome A Particles</t>
+  </si>
+  <si>
+    <t>Ceres Nanotrap Microbiome B Particles</t>
+  </si>
+  <si>
+    <t>Ceres Nanotrap Microbiome A &amp; B Particles</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Arial"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="16"/>
@@ -573,136 +586,137 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="49">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="1" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="14" fontId="2" fillId="5" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="13" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -929,7 +943,7 @@
   <sheetData>
     <row r="1" spans="1:26" ht="42" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B1" s="14" t="s">
         <v>0</v>
@@ -961,7 +975,7 @@
     </row>
     <row r="2" spans="1:26" ht="42" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B2" s="16" t="s">
         <v>10</v>
@@ -1025,7 +1039,7 @@
     </row>
     <row r="4" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>15</v>
@@ -1089,10 +1103,10 @@
     </row>
     <row r="6" spans="1:26" ht="30" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1"/>
       <c r="D6" s="1"/>
@@ -1121,7 +1135,7 @@
     </row>
     <row r="7" spans="1:26" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A7" s="17" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B7" s="18"/>
       <c r="C7" s="1"/>
@@ -1218,7 +1232,7 @@
         <v>13</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>18</v>
+        <v>67</v>
       </c>
       <c r="C10" s="1"/>
       <c r="D10" s="1"/>
@@ -1250,7 +1264,7 @@
         <v>14</v>
       </c>
       <c r="B11" s="17" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C11" s="1"/>
       <c r="D11" s="1"/>
@@ -30159,17 +30173,17 @@
       </c>
     </row>
     <row r="2" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="46" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="23"/>
-      <c r="C2" s="26"/>
-      <c r="D2" s="23"/>
-      <c r="E2" s="26"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="26"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="25"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="25"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="25"/>
       <c r="H2" s="47" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="I2" s="48"/>
       <c r="J2" s="48"/>
@@ -30177,15 +30191,15 @@
       <c r="L2" s="48"/>
     </row>
     <row r="3" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A3" s="22"/>
-      <c r="B3" s="25"/>
-      <c r="C3" s="29"/>
-      <c r="D3" s="25"/>
-      <c r="E3" s="30"/>
-      <c r="F3" s="25"/>
-      <c r="G3" s="30"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="29"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="I3" s="48"/>
       <c r="J3" s="48"/>
@@ -30193,15 +30207,15 @@
       <c r="L3" s="48"/>
     </row>
     <row r="4" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="22"/>
-      <c r="B4" s="24"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="24"/>
-      <c r="E4" s="27"/>
-      <c r="F4" s="24"/>
-      <c r="G4" s="27"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="23"/>
+      <c r="C4" s="27"/>
+      <c r="D4" s="23"/>
+      <c r="E4" s="26"/>
+      <c r="F4" s="23"/>
+      <c r="G4" s="26"/>
       <c r="H4" s="47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="I4" s="48"/>
       <c r="J4" s="48"/>
@@ -30209,91 +30223,91 @@
       <c r="L4" s="48"/>
     </row>
     <row r="5" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="46" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="39"/>
-      <c r="C5" s="31"/>
-      <c r="D5" s="39"/>
-      <c r="E5" s="31"/>
-      <c r="F5" s="39"/>
-      <c r="G5" s="31"/>
+      <c r="B5" s="38"/>
+      <c r="C5" s="30"/>
+      <c r="D5" s="38"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="38"/>
+      <c r="G5" s="30"/>
     </row>
     <row r="6" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A6" s="22"/>
-      <c r="B6" s="40"/>
-      <c r="C6" s="33"/>
-      <c r="D6" s="40"/>
-      <c r="E6" s="35"/>
-      <c r="F6" s="40"/>
-      <c r="G6" s="35"/>
+      <c r="A6" s="46"/>
+      <c r="B6" s="39"/>
+      <c r="C6" s="32"/>
+      <c r="D6" s="39"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="39"/>
+      <c r="G6" s="34"/>
     </row>
     <row r="7" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A7" s="22"/>
-      <c r="B7" s="41"/>
-      <c r="C7" s="36"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="41"/>
-      <c r="G7" s="38"/>
+      <c r="A7" s="46"/>
+      <c r="B7" s="40"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="40"/>
+      <c r="E7" s="37"/>
+      <c r="F7" s="40"/>
+      <c r="G7" s="37"/>
     </row>
     <row r="8" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A8" s="22" t="s">
+      <c r="A8" s="46" t="s">
         <v>5</v>
       </c>
-      <c r="B8" s="23"/>
-      <c r="C8" s="42"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="42"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="42"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="31"/>
+      <c r="E8" s="41"/>
+      <c r="F8" s="31"/>
+      <c r="G8" s="41"/>
     </row>
     <row r="9" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A9" s="22"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="45"/>
-      <c r="D9" s="34"/>
-      <c r="E9" s="43"/>
-      <c r="F9" s="34"/>
-      <c r="G9" s="43"/>
+      <c r="A9" s="46"/>
+      <c r="B9" s="24"/>
+      <c r="C9" s="44"/>
+      <c r="D9" s="33"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="33"/>
+      <c r="G9" s="42"/>
     </row>
     <row r="10" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A10" s="22"/>
-      <c r="B10" s="24"/>
-      <c r="C10" s="46"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="44"/>
-      <c r="F10" s="37"/>
-      <c r="G10" s="44"/>
+      <c r="A10" s="46"/>
+      <c r="B10" s="23"/>
+      <c r="C10" s="45"/>
+      <c r="D10" s="36"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="36"/>
+      <c r="G10" s="43"/>
     </row>
     <row r="11" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A11" s="22" t="s">
+      <c r="A11" s="46" t="s">
         <v>6</v>
       </c>
-      <c r="B11" s="39"/>
-      <c r="C11" s="31"/>
-      <c r="D11" s="39"/>
-      <c r="E11" s="31"/>
-      <c r="F11" s="39"/>
-      <c r="G11" s="31"/>
+      <c r="B11" s="38"/>
+      <c r="C11" s="30"/>
+      <c r="D11" s="38"/>
+      <c r="E11" s="30"/>
+      <c r="F11" s="38"/>
+      <c r="G11" s="30"/>
     </row>
     <row r="12" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="22"/>
-      <c r="B12" s="40"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="40"/>
-      <c r="E12" s="35"/>
-      <c r="F12" s="40"/>
-      <c r="G12" s="35"/>
+      <c r="A12" s="46"/>
+      <c r="B12" s="39"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="39"/>
+      <c r="E12" s="34"/>
+      <c r="F12" s="39"/>
+      <c r="G12" s="34"/>
     </row>
     <row r="13" spans="1:12" ht="35" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A13" s="22"/>
-      <c r="B13" s="41"/>
-      <c r="C13" s="36"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="38"/>
-      <c r="F13" s="41"/>
-      <c r="G13" s="38"/>
+      <c r="A13" s="46"/>
+      <c r="B13" s="40"/>
+      <c r="C13" s="35"/>
+      <c r="D13" s="40"/>
+      <c r="E13" s="37"/>
+      <c r="F13" s="40"/>
+      <c r="G13" s="37"/>
     </row>
     <row r="14" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="15" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -34409,10 +34423,10 @@
         <v>8</v>
       </c>
       <c r="C1" s="20" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D1" s="20" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="2" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -34420,13 +34434,13 @@
         <v>16</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>18</v>
+        <v>68</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D2" s="19" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
@@ -34434,169 +34448,172 @@
         <v>17</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>19</v>
+        <v>69</v>
       </c>
       <c r="C3" s="19" t="s">
+        <v>27</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="49" t="s">
+        <v>23</v>
+      </c>
+      <c r="B4" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="21" t="s">
+        <v>28</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="B5" s="7" t="s">
+        <v>9</v>
+      </c>
+      <c r="C5" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D5" s="19" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C6" s="19" t="s">
+        <v>30</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C7" s="21" t="s">
+        <v>31</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C8" s="19" t="s">
+        <v>32</v>
+      </c>
+      <c r="D8" s="19" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A4" s="19" t="s">
-        <v>25</v>
+    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C9" s="19" t="s">
+        <v>33</v>
       </c>
-      <c r="B4" s="7" t="s">
-        <v>9</v>
+      <c r="D9" s="19" t="s">
+        <v>58</v>
       </c>
-      <c r="C4" s="21" t="s">
-        <v>30</v>
+    </row>
+    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C10" s="21" t="s">
+        <v>34</v>
       </c>
-      <c r="D4" s="19" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C5" s="19" t="s">
-        <v>31</v>
-      </c>
-      <c r="D5" s="19" t="s">
+      <c r="D10" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C6" s="19" t="s">
-        <v>32</v>
+    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C11" s="21" t="s">
+        <v>35</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D11" s="19" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="7" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C7" s="21" t="s">
-        <v>33</v>
+    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C12" s="19" t="s">
+        <v>36</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D12" s="19" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="8" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C8" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="D8" s="19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="9" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C9" s="19" t="s">
-        <v>35</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="10" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C10" s="21" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="19" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="11" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C11" s="21" t="s">
+    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C13" s="19" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="19" t="s">
-        <v>65</v>
+      <c r="D13" s="19" t="s">
+        <v>51</v>
       </c>
     </row>
-    <row r="12" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C12" s="19" t="s">
+    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C14" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="D12" s="19" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C13" s="19" t="s">
+    </row>
+    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C15" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D13" s="19" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="14" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C14" s="19" t="s">
+    </row>
+    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C16" s="19" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C15" s="19" t="s">
+    <row r="17" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C17" s="19" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:4" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C16" s="19" t="s">
+    <row r="18" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C18" s="21" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="17" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C17" s="19" t="s">
+    <row r="19" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C19" s="19" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="18" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C18" s="21" t="s">
+    <row r="20" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C20" s="19" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C19" s="19" t="s">
+    <row r="21" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C21" s="21" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="20" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C20" s="19" t="s">
+    <row r="22" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C22" s="21" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="21" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C21" s="21" t="s">
+    <row r="23" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C23" s="21" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="22" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C22" s="21" t="s">
+    <row r="24" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C24" s="21" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="23" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C23" s="21" t="s">
+    <row r="25" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C25" s="21" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="24" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C24" s="21" t="s">
+    <row r="26" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="C26" s="19" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="25" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C25" s="21" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="26" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="C26" s="19" t="s">
-        <v>52</v>
-      </c>
-    </row>
     <row r="27" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="C27" s="19" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
     </row>
     <row r="28" spans="3:3" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -35573,6 +35590,7 @@
     <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
